--- a/feedback_forms/018_healthcare_patient_feedback_request_form--feedback_forms.xlsx
+++ b/feedback_forms/018_healthcare_patient_feedback_request_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>General Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>doctor_assisted</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Name of Doctor Assisted</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_visited</t>
+          <t>Date Visited</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>name_of_doctor</t>
+          <t>Name of Doctor</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>name_of_doctor_assisted</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>name_of_doctor</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Satisfaction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,40 +722,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>satisfaction</t>
+          <t>rating_comment</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>prophets</t>
+          <t>Rating Comment</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Follow-up</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rating_comment</t>
+          <t>contact_again</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rating_comment</t>
+          <t>Contact Again</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_again</t>
+          <t>name_of_clinic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>contact_again</t>
+          <t>Name of Clinic</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>name_of_hospital</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>additional_comments</t>
+          <t>Name of Hospital</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>name_of_clinic</t>
+          <t>department</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>name_of_clinic</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>name_of_hospital</t>
+          <t>doctor_specialty</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>name_of_hospital</t>
+          <t>Doctor Specialty</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,58 +911,58 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>patient_id</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>Patient ID</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>doctor_specialty</t>
+          <t>visit_date</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>doctor_specialty</t>
+          <t>Visit Date</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>patient_id</t>
+          <t>visit_time</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>patient_id</t>
+          <t>Visit Time</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,90 +975,86 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>visit_date</t>
+          <t>visit_duration</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>visit_date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+          <t>Visit Duration</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>visit_time</t>
+          <t>follow_up_date</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>visit_time</t>
+          <t>Follow-up Date</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>visit_duration</t>
+          <t>follow_up_time</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>visit_duration</t>
+          <t>Follow-up Time</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>follow_up_date</t>
+          <t>follow_up_contact</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>follow_up_date</t>
+          <t>Follow-up Contact</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1071,21 +1067,44 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>follow_up_time</t>
+          <t>patient_name</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>follow_up_time</t>
+          <t>Patient Name</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>visit_note</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Visit Note</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1105,9 +1124,9 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1130,119 +1149,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>prophets_choices</t>
+          <t>doctor_assisted_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent'}</t>
+          <t>dr_smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent'}</t>
+          <t>Dr Smith</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>prophets_choices</t>
+          <t>doctor_assisted_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good'}</t>
+          <t>dr_john</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good'}</t>
+          <t>Dr John</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>prophets_choices</t>
+          <t>doctor_assisted_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'satisfactory'}</t>
+          <t>dr_jane</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Satisfactory'}</t>
+          <t>Dr Jane</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>name_of_doctor_assisted_choices</t>
+          <t>doctor_assisted_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dr_smith'}</t>
+          <t>dr_alex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Dr Smith'}</t>
+          <t>Dr Alex</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>name_of_doctor_assisted_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dr_john'}</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Dr John'}</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>name_of_doctor_assisted_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dr_jane'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dr Jane'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>name_of_doctor_assisted_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'dr_alex'}</t>
+          <t>not</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Dr Alex'}</t>
+          <t>Not</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very',_'label':_'very',_'value':_5}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Very', 'label': 'Very', 'value': 5}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1271,165 +1290,165 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'label':_'good',_'value':_4}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'label': 'Good', 'value': 4}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not',_'label':_'not',_'value':_3}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not', 'label': 'Not', 'value': 3}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'fair',_'label':_'fair',_'value':_2}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Fair', 'label': 'Fair', 'value': 2}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>satisfaction_choices</t>
+          <t>follow_up_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'bad',_'label':_'bad',_'value':_1}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Bad', 'label': 'Bad', 'value': 1}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>contact_again_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>contact_again_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>follow_up_choices</t>
+          <t>contact_again_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>contact_again_choices</t>
+          <t>doctor_specialty_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>contact_again_choices</t>
+          <t>doctor_specialty_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>Neurology</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>contact_again_choices</t>
+          <t>doctor_specialty_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'unsure'}</t>
+          <t>orthopedic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'unsure'}</t>
+          <t>Orthopedic</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1460,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cardiology'}</t>
+          <t>pediatric</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'cardiology'}</t>
+          <t>Pediatric</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1477,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'neurology'}</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'neurology'}</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'orthopedic'}</t>
+          <t>oncology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'orthopedic'}</t>
+          <t>Oncology</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1511,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'pediatric'}</t>
+          <t>general_medicine</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'pediatric'}</t>
+          <t>General Medicine</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1528,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'surgery'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'surgery'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1545,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'oncology'}</t>
+          <t>gynecology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'oncology'}</t>
+          <t>Gynecology</t>
         </is>
       </c>
     </row>
@@ -1543,63 +1562,63 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'general_medicine'}</t>
+          <t>urology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'general_medicine'}</t>
+          <t>Urology</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>doctor_specialty_choices</t>
+          <t>follow_up_contact_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'dermatology'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'dermatology'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>doctor_specialty_choices</t>
+          <t>follow_up_contact_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'gynecology'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'gynecology'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>doctor_specialty_choices</t>
+          <t>follow_up_contact_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'urology'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'urology'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
